--- a/workspace/business-dd/work_overall/建設技術者派遣5社_セグメント比較_FY16-FY25.xlsx
+++ b/workspace/business-dd/work_overall/建設技術者派遣5社_セグメント比較_FY16-FY25.xlsx
@@ -1792,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1964,6 +1964,9 @@
       <c r="B13" t="str">
         <v>百万円</v>
       </c>
+      <c r="E13">
+        <v>8960</v>
+      </c>
       <c r="F13">
         <v>10819</v>
       </c>
@@ -1993,6 +1996,9 @@
       <c r="B14" t="str">
         <v>百万円</v>
       </c>
+      <c r="E14">
+        <v>895</v>
+      </c>
       <c r="F14">
         <v>1345</v>
       </c>
@@ -2022,6 +2028,9 @@
       <c r="B15" t="str">
         <v>%</v>
       </c>
+      <c r="E15">
+        <v>9.98</v>
+      </c>
       <c r="F15">
         <v>12.4</v>
       </c>
@@ -2138,63 +2147,71 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FY2019</v>
+        <v>FY2018</v>
       </c>
       <c r="B21" t="str">
-        <v>第13期有報抽出。単一セグメント開示のためサービス別建設売上は当時の収益認識注記が無く取得不可 (FY22から開示開始)。連結数値のみ。</v>
+        <v>IPO初年度(2018/3末上場)。連結業績はirbank.net公開データから補完。EDINET直接取得は提出時期外で未取得。</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FY2020</v>
+        <v>FY2019</v>
       </c>
       <c r="B22" t="str">
-        <v>第14期有報抽出。単一セグメント開示のためサービス別建設売上は当時の収益認識注記が無く取得不可 (FY22から開示開始)。連結数値のみ。</v>
+        <v>第13期有報抽出。単一セグメント開示のためサービス別建設売上は当時の収益認識注記が無く取得不可 (FY22から開示開始)。連結数値のみ。</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FY2021</v>
+        <v>FY2020</v>
       </c>
       <c r="B23" t="str">
-        <v>FY2021はサービス別補助開示なし。FY21は連結派遣技術者数の内訳も建設特定不可。</v>
+        <v>第14期有報抽出。単一セグメント開示のためサービス別建設売上は当時の収益認識注記が無く取得不可 (FY22から開示開始)。連結数値のみ。</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FY2022</v>
+        <v>FY2021</v>
       </c>
       <c r="B24" t="str">
-        <v>建設技術者派遣・紹介サービスの売上のみ収益認識注記から取得。営業利益・資産・設備投資・減価償却は単一セグメントのためサービス別開示なし。</v>
+        <v>FY2021はサービス別補助開示なし。FY21は連結派遣技術者数の内訳も建設特定不可。</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FY2023</v>
+        <v>FY2022</v>
       </c>
       <c r="B25" t="str">
-        <v>建設売上は収益認識注記から取得。サービス別の営業利益・設備投資はなし。</v>
+        <v>建設技術者派遣・紹介サービスの売上のみ収益認識注記から取得。営業利益・資産・設備投資・減価償却は単一セグメントのためサービス別開示なし。</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FY2024</v>
+        <v>FY2023</v>
       </c>
       <c r="B26" t="str">
-        <v>FY2024からサービス名称変更（機械設計開発→機電・半導体、SES→IT）。建設売上は収益認識注記から取得。</v>
+        <v>建設売上は収益認識注記から取得。サービス別の営業利益・設備投資はなし。</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v>FY2024</v>
+      </c>
+      <c r="B27" t="str">
+        <v>FY2024からサービス名称変更（機械設計開発→機電・半導体、SES→IT）。建設売上は収益認識注記から取得。</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
         <v>FY2025</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B28" t="str">
         <v>建設売上は収益認識注記から取得。建設構成比89.1%。サービス別の営業利益・資産・設備投資はなし。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2906,6 +2923,12 @@
       <c r="G14">
         <v>4666</v>
       </c>
+      <c r="H14">
+        <v>-25200</v>
+      </c>
+      <c r="I14">
+        <v>10100</v>
+      </c>
       <c r="J14">
         <v>12314</v>
       </c>
@@ -2938,6 +2961,12 @@
       <c r="G15">
         <v>5.7</v>
       </c>
+      <c r="H15">
+        <v>-25.5</v>
+      </c>
+      <c r="I15">
+        <v>6.8</v>
+      </c>
       <c r="J15">
         <v>8.2</v>
       </c>
@@ -3112,7 +3141,7 @@
         <v>FY2021</v>
       </c>
       <c r="B26" t="str">
-        <v>FY21はJGAAP開示（IFRS切替前）。連結粗利・売上はjppfs_corから取得。建設セグメント数値は規模が小さい点に留意（夢真HD合併が2021年）。連結営業利益は△271億円（合併に伴う非経常項目）でセグメント別は不開示。</v>
+        <v>FY21はJGAAP開示（IFRS切替前）。連結粗利・売上はjppfs_corから取得。建設セグメント数値は規模が小さい点に留意（夢真HD合併が2021年）。連結営業利益は△271億円（合併に伴う非経常項目）でセグメント別は不開示。 連結営業損失△252億は2021年4月の旧夢真HD合併に伴うのれん減損等の非経常項目 (irbank.net公開データ)。</v>
       </c>
     </row>
     <row r="27">
@@ -3120,7 +3149,7 @@
         <v>FY2022</v>
       </c>
       <c r="B27" t="str">
-        <v>IFRS適用開始（FY22から）。セグメント別営業利益は当期有報では未開示（FY23から開示開始）。</v>
+        <v>IFRS適用開始（FY22から）。セグメント別営業利益は当期有報では未開示（FY23から開示開始）。 連結営業利益101億 (irbank.net) - 経営統合一巡で正常化。</v>
       </c>
     </row>
     <row r="28">
@@ -3740,6 +3769,15 @@
       <c r="B14" t="str">
         <v>百万円</v>
       </c>
+      <c r="C14">
+        <v>8490</v>
+      </c>
+      <c r="D14">
+        <v>9650</v>
+      </c>
+      <c r="E14">
+        <v>11200</v>
+      </c>
       <c r="F14">
         <v>13739</v>
       </c>
@@ -3769,6 +3807,15 @@
       <c r="B15" t="str">
         <v>%</v>
       </c>
+      <c r="C15">
+        <v>9.4</v>
+      </c>
+      <c r="D15">
+        <v>9.64</v>
+      </c>
+      <c r="E15">
+        <v>9.64</v>
+      </c>
       <c r="F15">
         <v>9.5</v>
       </c>
@@ -3897,7 +3944,7 @@
         <v>FY2016</v>
       </c>
       <c r="B21" t="str">
-        <v>EDINETから第11期有報抽出。施工管理セグメント数値はセグメント情報注記から自動抽出（精度限定的、PDF確認推奨）。</v>
+        <v>EDINETから第11期有報抽出。施工管理セグメント数値はセグメント情報注記から自動抽出（精度限定的、PDF確認推奨）。 連結営業利益はirbank.net公開データから補完。</v>
       </c>
     </row>
     <row r="22">
@@ -3905,7 +3952,7 @@
         <v>FY2017</v>
       </c>
       <c r="B22" t="str">
-        <v>第12期有報抽出。施工管理セグメント数値はPDF確認が必要 (セグメント注記HTMLからの自動抽出は不可)。連結はJGAAP→IFRS移行期。</v>
+        <v>第12期有報抽出。施工管理セグメント数値はPDF確認が必要 (セグメント注記HTMLからの自動抽出は不可)。連結はJGAAP→IFRS移行期。 連結営業利益はirbank.net公開データから補完。</v>
       </c>
     </row>
     <row r="23">
@@ -3913,7 +3960,7 @@
         <v>FY2018</v>
       </c>
       <c r="B23" t="str">
-        <v>第13期有報抽出。施工管理セグメント数値はPDF確認が必要 (セグメント注記HTMLからの自動抽出は不可)。連結はJGAAP→IFRS移行期。</v>
+        <v>第13期有報抽出。施工管理セグメント数値はPDF確認が必要 (セグメント注記HTMLからの自動抽出は不可)。連結はJGAAP→IFRS移行期。 連結営業利益はirbank.net公開データから補完。</v>
       </c>
     </row>
     <row r="24">
@@ -6243,6 +6290,9 @@
       <c r="B5" t="str">
         <v>3月決算</v>
       </c>
+      <c r="E5">
+        <v>8960</v>
+      </c>
       <c r="F5">
         <v>10819</v>
       </c>
@@ -6716,6 +6766,9 @@
       <c r="B5" t="str">
         <v>3月決算</v>
       </c>
+      <c r="E5">
+        <v>895</v>
+      </c>
       <c r="F5">
         <v>1345</v>
       </c>
@@ -6780,6 +6833,12 @@
       <c r="G7">
         <v>4666</v>
       </c>
+      <c r="H7">
+        <v>-25200</v>
+      </c>
+      <c r="I7">
+        <v>10100</v>
+      </c>
       <c r="J7">
         <v>12314</v>
       </c>
@@ -6813,6 +6872,15 @@
       </c>
       <c r="B9" t="str">
         <v>6月決算</v>
+      </c>
+      <c r="C9">
+        <v>8490</v>
+      </c>
+      <c r="D9">
+        <v>9650</v>
+      </c>
+      <c r="E9">
+        <v>11200</v>
       </c>
       <c r="F9">
         <v>13739</v>
@@ -7168,6 +7236,9 @@
       <c r="B5" t="str">
         <v>3月決算</v>
       </c>
+      <c r="E5">
+        <v>9.98</v>
+      </c>
       <c r="F5">
         <v>12.4</v>
       </c>
@@ -7232,6 +7303,12 @@
       <c r="G7">
         <v>5.7</v>
       </c>
+      <c r="H7">
+        <v>-25.5</v>
+      </c>
+      <c r="I7">
+        <v>6.8</v>
+      </c>
       <c r="J7">
         <v>8.2</v>
       </c>
@@ -7265,6 +7342,15 @@
       </c>
       <c r="B9" t="str">
         <v>6月決算</v>
+      </c>
+      <c r="C9">
+        <v>9.4</v>
+      </c>
+      <c r="D9">
+        <v>9.64</v>
+      </c>
+      <c r="E9">
+        <v>9.64</v>
       </c>
       <c r="F9">
         <v>9.5</v>
